--- a/data/trans_camb/IP04F-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Clase-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 5,14</t>
+          <t>-15,68; 4,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 4,17</t>
+          <t>-13,32; 4,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 2,25</t>
+          <t>-12,15; 1,53</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 29,35</t>
+          <t>-51,49; 20,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,15; 32,86</t>
+          <t>-53,18; 30,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,87; 11,78</t>
+          <t>-46,67; 8,32</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 8,38</t>
+          <t>-7,55; 8,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 3,42</t>
+          <t>-13,44; 4,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 3,64</t>
+          <t>-8,29; 3,2</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,2; 84,31</t>
+          <t>-42,23; 82,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,04; 27,97</t>
+          <t>-57,95; 30,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 27,12</t>
+          <t>-42,39; 23,48</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 9,73</t>
+          <t>-6,33; 9,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 9,98</t>
+          <t>-0,68; 9,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 7,41</t>
+          <t>-2,4; 7,21</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,71; 169,44</t>
+          <t>-54,5; 169,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,22; —</t>
+          <t>-55,39; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 205,87</t>
+          <t>-33,84; 184,57</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,15</t>
+          <t>-4,57; 2,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,68</t>
+          <t>-1,52; 5,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,96</t>
+          <t>-2,19; 2,77</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,65; 59,8</t>
+          <t>-57,46; 62,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 171,9</t>
+          <t>-25,46; 173,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 68,92</t>
+          <t>-32,2; 64,75</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 4,09</t>
+          <t>-4,67; 4,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 1,42</t>
+          <t>-7,38; 1,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 1,16</t>
+          <t>-4,85; 1,45</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,76; 127,86</t>
+          <t>-62,73; 138,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 52,94</t>
+          <t>-80,23; 67,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 27,77</t>
+          <t>-63,05; 40,94</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 7,36</t>
+          <t>-10,77; 6,85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 0,58</t>
+          <t>-12,35; 0,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 1,83</t>
+          <t>-9,61; 1,24</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-72,18; 168,91</t>
+          <t>-73,78; 139,28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-91,65; 41,14</t>
+          <t>-92,01; 41,07</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,78; 36,47</t>
+          <t>-73,77; 28,73</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,46</t>
+          <t>-3,63; 1,68</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,43</t>
+          <t>-3,19; 1,58</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,74</t>
+          <t>-2,94; 0,68</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 17,75</t>
+          <t>-31,2; 19,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 19,09</t>
+          <t>-31,16; 20,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 8,2</t>
+          <t>-27,54; 7,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04F-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Clase-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 4,09</t>
+          <t>-15,52; 4,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 4,55</t>
+          <t>-13,02; 5,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 1,53</t>
+          <t>-12,06; 1,74</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,49; 20,34</t>
+          <t>-52,3; 26,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,18; 30,61</t>
+          <t>-53,02; 45,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,67; 8,32</t>
+          <t>-46,45; 8,99</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 8,08</t>
+          <t>-7,1; 8,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 4,03</t>
+          <t>-13,51; 3,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 3,2</t>
+          <t>-8,85; 3,82</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 82,23</t>
+          <t>-37,96; 82,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 30,0</t>
+          <t>-54,98; 25,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 23,48</t>
+          <t>-43,53; 28,36</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 9,75</t>
+          <t>-6,45; 9,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 9,68</t>
+          <t>-0,83; 8,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 7,21</t>
+          <t>-2,45; 7,28</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,5; 169,49</t>
+          <t>-56,86; 170,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,39; —</t>
+          <t>-53,46; 1059,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 184,57</t>
+          <t>-37,47; 178,68</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 2,44</t>
+          <t>-4,45; 2,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 5,63</t>
+          <t>-1,77; 5,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,77</t>
+          <t>-2,23; 2,84</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,46; 62,43</t>
+          <t>-56,88; 66,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 173,37</t>
+          <t>-30,55; 160,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 64,75</t>
+          <t>-32,04; 67,23</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 4,05</t>
+          <t>-4,86; 4,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 1,57</t>
+          <t>-7,11; 1,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 1,45</t>
+          <t>-4,81; 1,46</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-62,73; 138,17</t>
+          <t>-65,38; 120,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-80,23; 67,23</t>
+          <t>-81,77; 46,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,05; 40,94</t>
+          <t>-65,03; 36,26</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 6,85</t>
+          <t>-10,99; 6,14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 0,19</t>
+          <t>-12,61; 0,86</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 1,24</t>
+          <t>-9,75; 0,61</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,78; 139,28</t>
+          <t>-73,53; 122,53</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-92,01; 41,07</t>
+          <t>-91,91; 69,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,77; 28,73</t>
+          <t>-72,49; 18,58</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,68</t>
+          <t>-3,62; 1,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,58</t>
+          <t>-3,51; 1,31</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 0,68</t>
+          <t>-2,97; 0,67</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,2; 19,72</t>
+          <t>-31,61; 18,99</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 20,71</t>
+          <t>-34,59; 17,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 7,97</t>
+          <t>-27,28; 7,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04F-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Clase-trans_camb.xlsx
@@ -495,12 +495,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-4,4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>-5,67</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 4,92</t>
+          <t>-14,38; 4,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 5,83</t>
+          <t>-15,14; 5,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 1,74</t>
+          <t>-11,84; 2,25</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-21,41%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>-22,49%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-21,41%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,3; 26,49</t>
+          <t>-53,15; 32,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 45,69</t>
+          <t>-51,07; 29,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 8,99</t>
+          <t>-44,87; 11,78</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-4,64</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,26</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-4,64</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 8,42</t>
+          <t>-13,3; 3,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 3,48</t>
+          <t>-8,04; 8,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 3,82</t>
+          <t>-7,92; 3,64</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-24,63%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1,8%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-24,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,96; 82,53</t>
+          <t>-56,04; 27,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,98; 25,54</t>
+          <t>-44,2; 84,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 28,36</t>
+          <t>-40,47; 27,12</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,71</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>1,18</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,71</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 9,55</t>
+          <t>-0,99; 9,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 8,76</t>
+          <t>-7,09; 9,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 7,28</t>
+          <t>-2,41; 7,41</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>153,41%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>13,21%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>153,41%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,86; 170,19</t>
+          <t>-61,22; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,46; 1059,69</t>
+          <t>-59,71; 169,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 178,68</t>
+          <t>-35,02; 205,87</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,76</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>-1,02</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,51</t>
+          <t>-1,59; 5,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 5,61</t>
+          <t>-4,99; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,84</t>
+          <t>-2,31; 2,96</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>34,77%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>-17,23%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,88; 66,43</t>
+          <t>-25,8; 171,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 160,35</t>
+          <t>-58,65; 59,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 67,23</t>
+          <t>-34,32; 68,92</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,74</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>-0,41</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-2,74</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 4,09</t>
+          <t>-7,49; 1,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 1,12</t>
+          <t>-5,11; 4,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 1,46</t>
+          <t>-4,61; 1,16</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-45,54%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>-7,31%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-45,54%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,38; 120,67</t>
+          <t>-83,34; 52,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-81,77; 46,21</t>
+          <t>-66,76; 127,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 36,26</t>
+          <t>-61,17; 27,77</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-5,74</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>-1,8</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-5,74</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 6,14</t>
+          <t>-12,06; 0,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 0,86</t>
+          <t>-10,9; 7,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 0,61</t>
+          <t>-9,2; 1,83</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-63,72%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>-17,6%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-63,72%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,53; 122,53</t>
+          <t>-91,65; 41,14</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-91,91; 69,41</t>
+          <t>-72,18; 168,91</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-72,49; 18,58</t>
+          <t>-73,78; 36,47</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,94</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>-1,17</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 1,6</t>
+          <t>-3,47; 1,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,31</t>
+          <t>-3,68; 1,46</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,67</t>
+          <t>-2,86; 0,74</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-10,24%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>-11,32%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-10,24%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 18,99</t>
+          <t>-33,14; 19,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,59; 17,33</t>
+          <t>-31,37; 17,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,28; 7,78</t>
+          <t>-27,44; 8,2</t>
         </is>
       </c>
     </row>
